--- a/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Cars/AverageFlowDiscrepanciesReport.xlsx
+++ b/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Cars/AverageFlowDiscrepanciesReport.xlsx
@@ -1,39 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20415"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rm77\Desktop\Test\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FA17F6-D5E0-447C-AA5D-5DA2AF7C72DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Р›РёСЃС‚1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Rows">Лист1!$A$6:$M$7</definedName>
+    <definedName name="Rows">Р›РёСЃС‚1!$A$6:$Q$7</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Отчет по расходу топлива за период {{StartDate.ToString("dd-MM-yyyy")}} – {{EndDate.ToString("dd-MM-yyyy")}}</t>
   </si>
   <si>
-    <t>Выбраные авто:</t>
+    <t>Выбранные авто:</t>
   </si>
   <si>
     <t>{{SelectedCars}}</t>
@@ -48,9 +50,21 @@
     <t>Авто</t>
   </si>
   <si>
+    <t>Тип автомобиля</t>
+  </si>
+  <si>
+    <t>ФИО последнего водителя</t>
+  </si>
+  <si>
+    <t>Прикрепление к площадке</t>
+  </si>
+  <si>
     <t>Дата калибровки</t>
   </si>
   <si>
+    <t>Дата след.калибровки</t>
+  </si>
+  <si>
     <t>Начальный баланс</t>
   </si>
   <si>
@@ -60,6 +74,12 @@
     <t>Сумма км</t>
   </si>
   <si>
+    <t>Пересчитанный километраж</t>
+  </si>
+  <si>
+    <t>Полезный пробег, %</t>
+  </si>
+  <si>
     <t>Факт расход</t>
   </si>
   <si>
@@ -69,9 +89,6 @@
     <t>Разница</t>
   </si>
   <si>
-    <t>Разница, руб</t>
-  </si>
-  <si>
     <t>Факт расход на 100км</t>
   </si>
   <si>
@@ -84,9 +101,21 @@
     <t>{{item.Car}}</t>
   </si>
   <si>
+    <t>{{item.CarTypeOfUseString}}</t>
+  </si>
+  <si>
+    <t>{{item.DriverFullName}}</t>
+  </si>
+  <si>
+    <t>{{item.GeographicGroups}}</t>
+  </si>
+  <si>
     <t>{{item.CalibrationDate}}</t>
   </si>
   <si>
+    <t>{{item.NextCalibrationDate}}</t>
+  </si>
+  <si>
     <t>{{item.CurrentBalance}}</t>
   </si>
   <si>
@@ -96,6 +125,12 @@
     <t>{{item.ConfirmedDistance}}</t>
   </si>
   <si>
+    <t>{{item.RecalculatedDistance}}</t>
+  </si>
+  <si>
+    <t>{{item.UsefulMileagePercentValue}}</t>
+  </si>
+  <si>
     <t>{{item.ConsumptionFact}}</t>
   </si>
   <si>
@@ -105,9 +140,6 @@
     <t>{{item.DiscrepancyFuel}}</t>
   </si>
   <si>
-    <t>{{item.DiscrepancyMoney}}</t>
-  </si>
-  <si>
     <t>{{item.Consumption100KmFact}}</t>
   </si>
   <si>
@@ -115,24 +147,24 @@
   </si>
   <si>
     <t>{{item.DiscrepancyPercent}}</t>
-  </si>
-  <si>
-    <t>Дата след.калибровки</t>
-  </si>
-  <si>
-    <t>{{item.NextCalibrationDate}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="#\ ##0.0"/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -156,37 +188,352 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -209,108 +556,366 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFCAEEA6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFCAEEA6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF7C80"/>
         </patternFill>
       </fill>
     </dxf>
@@ -318,17 +923,14 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFCAEEA6"/>
-      <color rgb="FFFF7C80"/>
-      <color rgb="FFFFFFCC"/>
+      <color rgb="00CAEEA6"/>
+      <color rgb="00FF7C80"/>
+      <color rgb="00FFFFCC"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -377,17 +979,17 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -504,86 +1106,93 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMK13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="3" width="20.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="16.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" style="3" customWidth="1"/>
-    <col min="13" max="13" width="18.85546875" style="3" customWidth="1"/>
-    <col min="14" max="1025" width="9.140625" style="3"/>
+    <col min="1" max="1" width="10.7142857142857" style="2" customWidth="1"/>
+    <col min="2" max="4" width="20.5714285714286" style="2" customWidth="1"/>
+    <col min="5" max="6" width="16.5714285714286" style="2" customWidth="1"/>
+    <col min="7" max="8" width="16.8571428571429" style="2" customWidth="1"/>
+    <col min="9" max="10" width="22" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.1428571428571" style="2" customWidth="1"/>
+    <col min="12" max="17" width="17.7142857142857" style="3" customWidth="1"/>
+    <col min="18" max="1025" width="9.14285714285714" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="18.75" customHeight="1" spans="1:17">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="17.25" customHeight="1" spans="1:17">
       <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
     </row>
-    <row r="3" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="17.25" customHeight="1" spans="1:17">
       <c r="A3" s="4"/>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -593,140 +1202,164 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:15" s="11" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="5" s="1" customFormat="1" ht="21" spans="1:17">
       <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" outlineLevel="1" spans="1:17">
+      <c r="A6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>16</v>
+      <c r="I6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="14"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+    <row r="7" spans="1:17">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
+      <c r="J7" s="12"/>
       <c r="K7" s="12"/>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E13" s="15"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C3:M3"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="C2:M2"/>
+    <mergeCell ref="E1:Q1"/>
+    <mergeCell ref="C2:Q2"/>
+    <mergeCell ref="C3:Q3"/>
   </mergeCells>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>AND(ABS($A$9) &gt; B9, B9 &gt;8)</formula>
+  <conditionalFormatting sqref="A6:Q6">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>($F6="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:M6">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>($C6="")</formula>
+  <conditionalFormatting sqref="Q6">
+    <cfRule type="expression" dxfId="1" priority="7">
+      <formula>AND(ABS(Q6)&lt;=$C$3,ABS(Q6)&gt;=$C$3*(-1))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M6">
-    <cfRule type="expression" dxfId="2" priority="7">
-      <formula>AND(ABS( M6) &lt;= $C$3, ABS( M6) &gt;= $C$3 * (-1))</formula>
+    <cfRule type="expression" dxfId="2" priority="8">
+      <formula>AND(Q6&lt;0,ABS(Q6)&gt;=$C$3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="8">
-      <formula>AND(M6 &lt; 0, ABS( M6) &gt;= $C$3)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="9">
-      <formula>($C6&lt;&gt;"")</formula>
+    <cfRule type="expression" dxfId="3" priority="9">
+      <formula>($F6&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Cars/AverageFlowDiscrepanciesReport.xlsx
+++ b/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Cars/AverageFlowDiscrepanciesReport.xlsx
@@ -155,9 +155,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;РІвЂљР…&quot;_-;\-* #\.##0.00\ &quot;РІвЂљР…&quot;_-;_-* \-??\ &quot;РІвЂљР…&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;РІвЂљР…&quot;_-;\-* #\.##0\ &quot;РІвЂљР…&quot;_-;_-* \-\ &quot;РІвЂљР…&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="#\ ##0.0"/>
   </numFmts>
   <fonts count="24">
@@ -802,93 +802,108 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="right" wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
+    <cellStyle name="Р С›Р В±РЎвЂ№РЎвЂЎР Р…РЎвЂ№Р в„–" xfId="0" builtinId="0"/>
+    <cellStyle name="Р вЂ”Р В°Р С—РЎРЏРЎвЂљР В°РЎРЏ" xfId="1" builtinId="3"/>
+    <cellStyle name="Р вЂќР ВµР Р…Р ВµР В¶Р Р…РЎвЂ№Р в„–" xfId="2" builtinId="4"/>
+    <cellStyle name="Р СџРЎР‚Р С•РЎвЂ Р ВµР Р…РЎвЂљ" xfId="3" builtinId="5"/>
+    <cellStyle name="Р вЂ”Р В°Р С—РЎРЏРЎвЂљР В°РЎРЏ [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Р вЂќР ВµР Р…Р ВµР В¶Р Р…РЎвЂ№Р в„– [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Р вЂњР С‘Р С—Р ВµРЎР‚РЎРѓРЎРѓРЎвЂ№Р В»Р С”Р В°" xfId="6" builtinId="8"/>
+    <cellStyle name="Р С›РЎвЂљР С”РЎР‚РЎвЂ№Р Р†Р В°Р Р†РЎв‚¬Р В°РЎРЏРЎРѓРЎРЏ Р С–Р С‘Р С—Р ВµРЎР‚РЎРѓРЎРѓРЎвЂ№Р В»Р С”Р В°" xfId="7" builtinId="9"/>
+    <cellStyle name="Р СџРЎР‚Р С‘Р СР ВµРЎвЂЎР В°Р Р…Р С‘Р Вµ" xfId="8" builtinId="10"/>
+    <cellStyle name="Р СџРЎР‚Р ВµР Т‘РЎС“Р С—РЎР‚Р ВµР В¶Р Т‘Р В°РЎР‹РЎвЂ°Р С‘Р в„– РЎвЂљР ВµР С”РЎРѓРЎвЂљ" xfId="9" builtinId="11"/>
+    <cellStyle name="Р вЂ”Р В°Р С–Р С•Р В»Р С•Р Р†Р С•Р С”" xfId="10" builtinId="15"/>
+    <cellStyle name="Р СџР С•РЎРЏРЎРѓР Р…Р С‘РЎвЂљР ВµР В»РЎРЉР Р…РЎвЂ№Р в„– РЎвЂљР ВµР С”РЎРѓРЎвЂљ" xfId="11" builtinId="53"/>
+    <cellStyle name="Р вЂ”Р В°Р С–Р С•Р В»Р С•Р Р†Р С•Р С” 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Р вЂ”Р В°Р С–Р С•Р В»Р С•Р Р†Р С•Р С” 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Р вЂ”Р В°Р С–Р С•Р В»Р С•Р Р†Р С•Р С” 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Р вЂ”Р В°Р С–Р С•Р В»Р С•Р Р†Р С•Р С” 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Р вЂ™Р Р†Р С•Р Т‘" xfId="16" builtinId="20"/>
+    <cellStyle name="Р вЂ™РЎвЂ№Р Р†Р С•Р Т‘" xfId="17" builtinId="21"/>
+    <cellStyle name="Р вЂ™РЎвЂ№РЎвЂЎР С‘РЎРѓР В»Р ВµР Р…Р С‘Р Вµ" xfId="18" builtinId="22"/>
+    <cellStyle name="Р СџРЎР‚Р С•Р Р†Р ВµРЎР‚Р С‘РЎвЂљРЎРЉ РЎРЏРЎвЂЎР ВµР в„–Р С”РЎС“" xfId="19" builtinId="23"/>
+    <cellStyle name="Р РЋР Р†РЎРЏР В·Р В°Р Р…Р Р…Р В°РЎРЏ РЎРЏРЎвЂЎР ВµР в„–Р С”Р В°" xfId="20" builtinId="24"/>
+    <cellStyle name="Р ВРЎвЂљР С•Р С–Р С•" xfId="21" builtinId="25"/>
+    <cellStyle name="Р ТђР С•РЎР‚Р С•РЎв‚¬Р С‘Р в„–" xfId="22" builtinId="26"/>
+    <cellStyle name="Р СџР В»Р С•РЎвЂ¦Р С•Р в„–" xfId="23" builtinId="27"/>
+    <cellStyle name="Р СњР ВµР в„–РЎвЂљРЎР‚Р В°Р В»РЎРЉР Р…РЎвЂ№Р в„–" xfId="24" builtinId="28"/>
+    <cellStyle name="Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ1" xfId="25" builtinId="29"/>
+    <cellStyle name="20%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ1" xfId="26" builtinId="30"/>
+    <cellStyle name="40%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ1" xfId="27" builtinId="31"/>
+    <cellStyle name="60%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ1" xfId="28" builtinId="32"/>
+    <cellStyle name="Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ2" xfId="29" builtinId="33"/>
+    <cellStyle name="20%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ2" xfId="30" builtinId="34"/>
+    <cellStyle name="40%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ2" xfId="31" builtinId="35"/>
+    <cellStyle name="60%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ2" xfId="32" builtinId="36"/>
+    <cellStyle name="Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ3" xfId="33" builtinId="37"/>
+    <cellStyle name="20%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ3" xfId="34" builtinId="38"/>
+    <cellStyle name="40%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ3" xfId="35" builtinId="39"/>
+    <cellStyle name="60%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ3" xfId="36" builtinId="40"/>
+    <cellStyle name="Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ4" xfId="37" builtinId="41"/>
+    <cellStyle name="20%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ4" xfId="38" builtinId="42"/>
+    <cellStyle name="40%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ4" xfId="39" builtinId="43"/>
+    <cellStyle name="60%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ4" xfId="40" builtinId="44"/>
+    <cellStyle name="Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ5" xfId="41" builtinId="45"/>
+    <cellStyle name="20%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ5" xfId="42" builtinId="46"/>
+    <cellStyle name="40%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ5" xfId="43" builtinId="47"/>
+    <cellStyle name="60%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ5" xfId="44" builtinId="48"/>
+    <cellStyle name="Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ6" xfId="45" builtinId="49"/>
+    <cellStyle name="20%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ6" xfId="46" builtinId="50"/>
+    <cellStyle name="40%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ6" xfId="47" builtinId="51"/>
+    <cellStyle name="60%Р’В РІР‚вЂќ Р С’Р С”РЎвЂ Р ВµР Р…РЎвЂљ6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -1112,229 +1127,1237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:AMK7"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="10.7142857142857" style="2" customWidth="1"/>
-    <col min="2" max="4" width="20.5714285714286" style="2" customWidth="1"/>
-    <col min="5" max="6" width="16.5714285714286" style="2" customWidth="1"/>
-    <col min="7" max="8" width="16.8571428571429" style="2" customWidth="1"/>
-    <col min="9" max="10" width="22" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.1428571428571" style="2" customWidth="1"/>
-    <col min="12" max="17" width="17.7142857142857" style="3" customWidth="1"/>
-    <col min="18" max="1025" width="9.14285714285714" style="3"/>
+    <col min="1" max="1" width="10.7142857142857" style="3" customWidth="1"/>
+    <col min="2" max="4" width="20.5714285714286" style="3" customWidth="1"/>
+    <col min="5" max="6" width="16.5714285714286" style="3" customWidth="1"/>
+    <col min="7" max="8" width="16.8571428571429" style="3" customWidth="1"/>
+    <col min="9" max="10" width="22" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.1428571428571" style="3" customWidth="1"/>
+    <col min="12" max="17" width="17.7142857142857" style="4" customWidth="1"/>
+    <col min="18" max="1025" width="9.14285714285714" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:17">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="5" t="s">
+    <row r="1" ht="18.75" customHeight="1" spans="1:1024 1025:1025">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
     </row>
-    <row r="2" ht="17.25" customHeight="1" spans="1:17">
-      <c r="A2" s="4"/>
-      <c r="B2" s="6" t="s">
+    <row r="2" ht="17.25" customHeight="1" spans="1:1024 1025:1025">
+      <c r="A2" s="5"/>
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:17">
-      <c r="A3" s="4"/>
-      <c r="B3" s="6" t="s">
+    <row r="3" ht="17.25" customHeight="1" spans="1:1024 1025:1025">
+      <c r="A3" s="5"/>
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
     </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+    <row r="4" spans="1:1024 1025:1025">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="21" spans="1:17">
-      <c r="A5" s="9" t="s">
+    <row r="5" s="1" customFormat="1" ht="21" spans="1:1024 1025:1025">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="P5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q5" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" outlineLevel="1" spans="1:17">
-      <c r="A6" s="10" t="s">
+    <row r="6" s="2" customFormat="1" ht="33.75" outlineLevel="1" spans="1:1024 1025:1025">
+      <c r="A6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="P6" s="12" t="s">
+      <c r="P6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="12" t="s">
+      <c r="Q6" s="13" t="s">
         <v>38</v>
       </c>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="14"/>
+      <c r="AL6" s="14"/>
+      <c r="AM6" s="14"/>
+      <c r="AN6" s="14"/>
+      <c r="AO6" s="14"/>
+      <c r="AP6" s="14"/>
+      <c r="AQ6" s="14"/>
+      <c r="AR6" s="14"/>
+      <c r="AS6" s="14"/>
+      <c r="AT6" s="14"/>
+      <c r="AU6" s="14"/>
+      <c r="AV6" s="14"/>
+      <c r="AW6" s="14"/>
+      <c r="AX6" s="14"/>
+      <c r="AY6" s="14"/>
+      <c r="AZ6" s="14"/>
+      <c r="BA6" s="14"/>
+      <c r="BB6" s="14"/>
+      <c r="BC6" s="14"/>
+      <c r="BD6" s="14"/>
+      <c r="BE6" s="14"/>
+      <c r="BF6" s="14"/>
+      <c r="BG6" s="14"/>
+      <c r="BH6" s="14"/>
+      <c r="BI6" s="14"/>
+      <c r="BJ6" s="14"/>
+      <c r="BK6" s="14"/>
+      <c r="BL6" s="14"/>
+      <c r="BM6" s="14"/>
+      <c r="BN6" s="14"/>
+      <c r="BO6" s="14"/>
+      <c r="BP6" s="14"/>
+      <c r="BQ6" s="14"/>
+      <c r="BR6" s="14"/>
+      <c r="BS6" s="14"/>
+      <c r="BT6" s="14"/>
+      <c r="BU6" s="14"/>
+      <c r="BV6" s="14"/>
+      <c r="BW6" s="14"/>
+      <c r="BX6" s="14"/>
+      <c r="BY6" s="14"/>
+      <c r="BZ6" s="14"/>
+      <c r="CA6" s="14"/>
+      <c r="CB6" s="14"/>
+      <c r="CC6" s="14"/>
+      <c r="CD6" s="14"/>
+      <c r="CE6" s="14"/>
+      <c r="CF6" s="14"/>
+      <c r="CG6" s="14"/>
+      <c r="CH6" s="14"/>
+      <c r="CI6" s="14"/>
+      <c r="CJ6" s="14"/>
+      <c r="CK6" s="14"/>
+      <c r="CL6" s="14"/>
+      <c r="CM6" s="14"/>
+      <c r="CN6" s="14"/>
+      <c r="CO6" s="14"/>
+      <c r="CP6" s="14"/>
+      <c r="CQ6" s="14"/>
+      <c r="CR6" s="14"/>
+      <c r="CS6" s="14"/>
+      <c r="CT6" s="14"/>
+      <c r="CU6" s="14"/>
+      <c r="CV6" s="14"/>
+      <c r="CW6" s="14"/>
+      <c r="CX6" s="14"/>
+      <c r="CY6" s="14"/>
+      <c r="CZ6" s="14"/>
+      <c r="DA6" s="14"/>
+      <c r="DB6" s="14"/>
+      <c r="DC6" s="14"/>
+      <c r="DD6" s="14"/>
+      <c r="DE6" s="14"/>
+      <c r="DF6" s="14"/>
+      <c r="DG6" s="14"/>
+      <c r="DH6" s="14"/>
+      <c r="DI6" s="14"/>
+      <c r="DJ6" s="14"/>
+      <c r="DK6" s="14"/>
+      <c r="DL6" s="14"/>
+      <c r="DM6" s="14"/>
+      <c r="DN6" s="14"/>
+      <c r="DO6" s="14"/>
+      <c r="DP6" s="14"/>
+      <c r="DQ6" s="14"/>
+      <c r="DR6" s="14"/>
+      <c r="DS6" s="14"/>
+      <c r="DT6" s="14"/>
+      <c r="DU6" s="14"/>
+      <c r="DV6" s="14"/>
+      <c r="DW6" s="14"/>
+      <c r="DX6" s="14"/>
+      <c r="DY6" s="14"/>
+      <c r="DZ6" s="14"/>
+      <c r="EA6" s="14"/>
+      <c r="EB6" s="14"/>
+      <c r="EC6" s="14"/>
+      <c r="ED6" s="14"/>
+      <c r="EE6" s="14"/>
+      <c r="EF6" s="14"/>
+      <c r="EG6" s="14"/>
+      <c r="EH6" s="14"/>
+      <c r="EI6" s="14"/>
+      <c r="EJ6" s="14"/>
+      <c r="EK6" s="14"/>
+      <c r="EL6" s="14"/>
+      <c r="EM6" s="14"/>
+      <c r="EN6" s="14"/>
+      <c r="EO6" s="14"/>
+      <c r="EP6" s="14"/>
+      <c r="EQ6" s="14"/>
+      <c r="ER6" s="14"/>
+      <c r="ES6" s="14"/>
+      <c r="ET6" s="14"/>
+      <c r="EU6" s="14"/>
+      <c r="EV6" s="14"/>
+      <c r="EW6" s="14"/>
+      <c r="EX6" s="14"/>
+      <c r="EY6" s="14"/>
+      <c r="EZ6" s="14"/>
+      <c r="FA6" s="14"/>
+      <c r="FB6" s="14"/>
+      <c r="FC6" s="14"/>
+      <c r="FD6" s="14"/>
+      <c r="FE6" s="14"/>
+      <c r="FF6" s="14"/>
+      <c r="FG6" s="14"/>
+      <c r="FH6" s="14"/>
+      <c r="FI6" s="14"/>
+      <c r="FJ6" s="14"/>
+      <c r="FK6" s="14"/>
+      <c r="FL6" s="14"/>
+      <c r="FM6" s="14"/>
+      <c r="FN6" s="14"/>
+      <c r="FO6" s="14"/>
+      <c r="FP6" s="14"/>
+      <c r="FQ6" s="14"/>
+      <c r="FR6" s="14"/>
+      <c r="FS6" s="14"/>
+      <c r="FT6" s="14"/>
+      <c r="FU6" s="14"/>
+      <c r="FV6" s="14"/>
+      <c r="FW6" s="14"/>
+      <c r="FX6" s="14"/>
+      <c r="FY6" s="14"/>
+      <c r="FZ6" s="14"/>
+      <c r="GA6" s="14"/>
+      <c r="GB6" s="14"/>
+      <c r="GC6" s="14"/>
+      <c r="GD6" s="14"/>
+      <c r="GE6" s="14"/>
+      <c r="GF6" s="14"/>
+      <c r="GG6" s="14"/>
+      <c r="GH6" s="14"/>
+      <c r="GI6" s="14"/>
+      <c r="GJ6" s="14"/>
+      <c r="GK6" s="14"/>
+      <c r="GL6" s="14"/>
+      <c r="GM6" s="14"/>
+      <c r="GN6" s="14"/>
+      <c r="GO6" s="14"/>
+      <c r="GP6" s="14"/>
+      <c r="GQ6" s="14"/>
+      <c r="GR6" s="14"/>
+      <c r="GS6" s="14"/>
+      <c r="GT6" s="14"/>
+      <c r="GU6" s="14"/>
+      <c r="GV6" s="14"/>
+      <c r="GW6" s="14"/>
+      <c r="GX6" s="14"/>
+      <c r="GY6" s="14"/>
+      <c r="GZ6" s="14"/>
+      <c r="HA6" s="14"/>
+      <c r="HB6" s="14"/>
+      <c r="HC6" s="14"/>
+      <c r="HD6" s="14"/>
+      <c r="HE6" s="14"/>
+      <c r="HF6" s="14"/>
+      <c r="HG6" s="14"/>
+      <c r="HH6" s="14"/>
+      <c r="HI6" s="14"/>
+      <c r="HJ6" s="14"/>
+      <c r="HK6" s="14"/>
+      <c r="HL6" s="14"/>
+      <c r="HM6" s="14"/>
+      <c r="HN6" s="14"/>
+      <c r="HO6" s="14"/>
+      <c r="HP6" s="14"/>
+      <c r="HQ6" s="14"/>
+      <c r="HR6" s="14"/>
+      <c r="HS6" s="14"/>
+      <c r="HT6" s="14"/>
+      <c r="HU6" s="14"/>
+      <c r="HV6" s="14"/>
+      <c r="HW6" s="14"/>
+      <c r="HX6" s="14"/>
+      <c r="HY6" s="14"/>
+      <c r="HZ6" s="14"/>
+      <c r="IA6" s="14"/>
+      <c r="IB6" s="14"/>
+      <c r="IC6" s="14"/>
+      <c r="ID6" s="14"/>
+      <c r="IE6" s="14"/>
+      <c r="IF6" s="14"/>
+      <c r="IG6" s="14"/>
+      <c r="IH6" s="14"/>
+      <c r="II6" s="14"/>
+      <c r="IJ6" s="14"/>
+      <c r="IK6" s="14"/>
+      <c r="IL6" s="14"/>
+      <c r="IM6" s="14"/>
+      <c r="IN6" s="14"/>
+      <c r="IO6" s="14"/>
+      <c r="IP6" s="14"/>
+      <c r="IQ6" s="14"/>
+      <c r="IR6" s="14"/>
+      <c r="IS6" s="14"/>
+      <c r="IT6" s="14"/>
+      <c r="IU6" s="14"/>
+      <c r="IV6" s="14"/>
+      <c r="IW6" s="14"/>
+      <c r="IX6" s="14"/>
+      <c r="IY6" s="14"/>
+      <c r="IZ6" s="14"/>
+      <c r="JA6" s="14"/>
+      <c r="JB6" s="14"/>
+      <c r="JC6" s="14"/>
+      <c r="JD6" s="14"/>
+      <c r="JE6" s="14"/>
+      <c r="JF6" s="14"/>
+      <c r="JG6" s="14"/>
+      <c r="JH6" s="14"/>
+      <c r="JI6" s="14"/>
+      <c r="JJ6" s="14"/>
+      <c r="JK6" s="14"/>
+      <c r="JL6" s="14"/>
+      <c r="JM6" s="14"/>
+      <c r="JN6" s="14"/>
+      <c r="JO6" s="14"/>
+      <c r="JP6" s="14"/>
+      <c r="JQ6" s="14"/>
+      <c r="JR6" s="14"/>
+      <c r="JS6" s="14"/>
+      <c r="JT6" s="14"/>
+      <c r="JU6" s="14"/>
+      <c r="JV6" s="14"/>
+      <c r="JW6" s="14"/>
+      <c r="JX6" s="14"/>
+      <c r="JY6" s="14"/>
+      <c r="JZ6" s="14"/>
+      <c r="KA6" s="14"/>
+      <c r="KB6" s="14"/>
+      <c r="KC6" s="14"/>
+      <c r="KD6" s="14"/>
+      <c r="KE6" s="14"/>
+      <c r="KF6" s="14"/>
+      <c r="KG6" s="14"/>
+      <c r="KH6" s="14"/>
+      <c r="KI6" s="14"/>
+      <c r="KJ6" s="14"/>
+      <c r="KK6" s="14"/>
+      <c r="KL6" s="14"/>
+      <c r="KM6" s="14"/>
+      <c r="KN6" s="14"/>
+      <c r="KO6" s="14"/>
+      <c r="KP6" s="14"/>
+      <c r="KQ6" s="14"/>
+      <c r="KR6" s="14"/>
+      <c r="KS6" s="14"/>
+      <c r="KT6" s="14"/>
+      <c r="KU6" s="14"/>
+      <c r="KV6" s="14"/>
+      <c r="KW6" s="14"/>
+      <c r="KX6" s="14"/>
+      <c r="KY6" s="14"/>
+      <c r="KZ6" s="14"/>
+      <c r="LA6" s="14"/>
+      <c r="LB6" s="14"/>
+      <c r="LC6" s="14"/>
+      <c r="LD6" s="14"/>
+      <c r="LE6" s="14"/>
+      <c r="LF6" s="14"/>
+      <c r="LG6" s="14"/>
+      <c r="LH6" s="14"/>
+      <c r="LI6" s="14"/>
+      <c r="LJ6" s="14"/>
+      <c r="LK6" s="14"/>
+      <c r="LL6" s="14"/>
+      <c r="LM6" s="14"/>
+      <c r="LN6" s="14"/>
+      <c r="LO6" s="14"/>
+      <c r="LP6" s="14"/>
+      <c r="LQ6" s="14"/>
+      <c r="LR6" s="14"/>
+      <c r="LS6" s="14"/>
+      <c r="LT6" s="14"/>
+      <c r="LU6" s="14"/>
+      <c r="LV6" s="14"/>
+      <c r="LW6" s="14"/>
+      <c r="LX6" s="14"/>
+      <c r="LY6" s="14"/>
+      <c r="LZ6" s="14"/>
+      <c r="MA6" s="14"/>
+      <c r="MB6" s="14"/>
+      <c r="MC6" s="14"/>
+      <c r="MD6" s="14"/>
+      <c r="ME6" s="14"/>
+      <c r="MF6" s="14"/>
+      <c r="MG6" s="14"/>
+      <c r="MH6" s="14"/>
+      <c r="MI6" s="14"/>
+      <c r="MJ6" s="14"/>
+      <c r="MK6" s="14"/>
+      <c r="ML6" s="14"/>
+      <c r="MM6" s="14"/>
+      <c r="MN6" s="14"/>
+      <c r="MO6" s="14"/>
+      <c r="MP6" s="14"/>
+      <c r="MQ6" s="14"/>
+      <c r="MR6" s="14"/>
+      <c r="MS6" s="14"/>
+      <c r="MT6" s="14"/>
+      <c r="MU6" s="14"/>
+      <c r="MV6" s="14"/>
+      <c r="MW6" s="14"/>
+      <c r="MX6" s="14"/>
+      <c r="MY6" s="14"/>
+      <c r="MZ6" s="14"/>
+      <c r="NA6" s="14"/>
+      <c r="NB6" s="14"/>
+      <c r="NC6" s="14"/>
+      <c r="ND6" s="14"/>
+      <c r="NE6" s="14"/>
+      <c r="NF6" s="14"/>
+      <c r="NG6" s="14"/>
+      <c r="NH6" s="14"/>
+      <c r="NI6" s="14"/>
+      <c r="NJ6" s="14"/>
+      <c r="NK6" s="14"/>
+      <c r="NL6" s="14"/>
+      <c r="NM6" s="14"/>
+      <c r="NN6" s="14"/>
+      <c r="NO6" s="14"/>
+      <c r="NP6" s="14"/>
+      <c r="NQ6" s="14"/>
+      <c r="NR6" s="14"/>
+      <c r="NS6" s="14"/>
+      <c r="NT6" s="14"/>
+      <c r="NU6" s="14"/>
+      <c r="NV6" s="14"/>
+      <c r="NW6" s="14"/>
+      <c r="NX6" s="14"/>
+      <c r="NY6" s="14"/>
+      <c r="NZ6" s="14"/>
+      <c r="OA6" s="14"/>
+      <c r="OB6" s="14"/>
+      <c r="OC6" s="14"/>
+      <c r="OD6" s="14"/>
+      <c r="OE6" s="14"/>
+      <c r="OF6" s="14"/>
+      <c r="OG6" s="14"/>
+      <c r="OH6" s="14"/>
+      <c r="OI6" s="14"/>
+      <c r="OJ6" s="14"/>
+      <c r="OK6" s="14"/>
+      <c r="OL6" s="14"/>
+      <c r="OM6" s="14"/>
+      <c r="ON6" s="14"/>
+      <c r="OO6" s="14"/>
+      <c r="OP6" s="14"/>
+      <c r="OQ6" s="14"/>
+      <c r="OR6" s="14"/>
+      <c r="OS6" s="14"/>
+      <c r="OT6" s="14"/>
+      <c r="OU6" s="14"/>
+      <c r="OV6" s="14"/>
+      <c r="OW6" s="14"/>
+      <c r="OX6" s="14"/>
+      <c r="OY6" s="14"/>
+      <c r="OZ6" s="14"/>
+      <c r="PA6" s="14"/>
+      <c r="PB6" s="14"/>
+      <c r="PC6" s="14"/>
+      <c r="PD6" s="14"/>
+      <c r="PE6" s="14"/>
+      <c r="PF6" s="14"/>
+      <c r="PG6" s="14"/>
+      <c r="PH6" s="14"/>
+      <c r="PI6" s="14"/>
+      <c r="PJ6" s="14"/>
+      <c r="PK6" s="14"/>
+      <c r="PL6" s="14"/>
+      <c r="PM6" s="14"/>
+      <c r="PN6" s="14"/>
+      <c r="PO6" s="14"/>
+      <c r="PP6" s="14"/>
+      <c r="PQ6" s="14"/>
+      <c r="PR6" s="14"/>
+      <c r="PS6" s="14"/>
+      <c r="PT6" s="14"/>
+      <c r="PU6" s="14"/>
+      <c r="PV6" s="14"/>
+      <c r="PW6" s="14"/>
+      <c r="PX6" s="14"/>
+      <c r="PY6" s="14"/>
+      <c r="PZ6" s="14"/>
+      <c r="QA6" s="14"/>
+      <c r="QB6" s="14"/>
+      <c r="QC6" s="14"/>
+      <c r="QD6" s="14"/>
+      <c r="QE6" s="14"/>
+      <c r="QF6" s="14"/>
+      <c r="QG6" s="14"/>
+      <c r="QH6" s="14"/>
+      <c r="QI6" s="14"/>
+      <c r="QJ6" s="14"/>
+      <c r="QK6" s="14"/>
+      <c r="QL6" s="14"/>
+      <c r="QM6" s="14"/>
+      <c r="QN6" s="14"/>
+      <c r="QO6" s="14"/>
+      <c r="QP6" s="14"/>
+      <c r="QQ6" s="14"/>
+      <c r="QR6" s="14"/>
+      <c r="QS6" s="14"/>
+      <c r="QT6" s="14"/>
+      <c r="QU6" s="14"/>
+      <c r="QV6" s="14"/>
+      <c r="QW6" s="14"/>
+      <c r="QX6" s="14"/>
+      <c r="QY6" s="14"/>
+      <c r="QZ6" s="14"/>
+      <c r="RA6" s="14"/>
+      <c r="RB6" s="14"/>
+      <c r="RC6" s="14"/>
+      <c r="RD6" s="14"/>
+      <c r="RE6" s="14"/>
+      <c r="RF6" s="14"/>
+      <c r="RG6" s="14"/>
+      <c r="RH6" s="14"/>
+      <c r="RI6" s="14"/>
+      <c r="RJ6" s="14"/>
+      <c r="RK6" s="14"/>
+      <c r="RL6" s="14"/>
+      <c r="RM6" s="14"/>
+      <c r="RN6" s="14"/>
+      <c r="RO6" s="14"/>
+      <c r="RP6" s="14"/>
+      <c r="RQ6" s="14"/>
+      <c r="RR6" s="14"/>
+      <c r="RS6" s="14"/>
+      <c r="RT6" s="14"/>
+      <c r="RU6" s="14"/>
+      <c r="RV6" s="14"/>
+      <c r="RW6" s="14"/>
+      <c r="RX6" s="14"/>
+      <c r="RY6" s="14"/>
+      <c r="RZ6" s="14"/>
+      <c r="SA6" s="14"/>
+      <c r="SB6" s="14"/>
+      <c r="SC6" s="14"/>
+      <c r="SD6" s="14"/>
+      <c r="SE6" s="14"/>
+      <c r="SF6" s="14"/>
+      <c r="SG6" s="14"/>
+      <c r="SH6" s="14"/>
+      <c r="SI6" s="14"/>
+      <c r="SJ6" s="14"/>
+      <c r="SK6" s="14"/>
+      <c r="SL6" s="14"/>
+      <c r="SM6" s="14"/>
+      <c r="SN6" s="14"/>
+      <c r="SO6" s="14"/>
+      <c r="SP6" s="14"/>
+      <c r="SQ6" s="14"/>
+      <c r="SR6" s="14"/>
+      <c r="SS6" s="14"/>
+      <c r="ST6" s="14"/>
+      <c r="SU6" s="14"/>
+      <c r="SV6" s="14"/>
+      <c r="SW6" s="14"/>
+      <c r="SX6" s="14"/>
+      <c r="SY6" s="14"/>
+      <c r="SZ6" s="14"/>
+      <c r="TA6" s="14"/>
+      <c r="TB6" s="14"/>
+      <c r="TC6" s="14"/>
+      <c r="TD6" s="14"/>
+      <c r="TE6" s="14"/>
+      <c r="TF6" s="14"/>
+      <c r="TG6" s="14"/>
+      <c r="TH6" s="14"/>
+      <c r="TI6" s="14"/>
+      <c r="TJ6" s="14"/>
+      <c r="TK6" s="14"/>
+      <c r="TL6" s="14"/>
+      <c r="TM6" s="14"/>
+      <c r="TN6" s="14"/>
+      <c r="TO6" s="14"/>
+      <c r="TP6" s="14"/>
+      <c r="TQ6" s="14"/>
+      <c r="TR6" s="14"/>
+      <c r="TS6" s="14"/>
+      <c r="TT6" s="14"/>
+      <c r="TU6" s="14"/>
+      <c r="TV6" s="14"/>
+      <c r="TW6" s="14"/>
+      <c r="TX6" s="14"/>
+      <c r="TY6" s="14"/>
+      <c r="TZ6" s="14"/>
+      <c r="UA6" s="14"/>
+      <c r="UB6" s="14"/>
+      <c r="UC6" s="14"/>
+      <c r="UD6" s="14"/>
+      <c r="UE6" s="14"/>
+      <c r="UF6" s="14"/>
+      <c r="UG6" s="14"/>
+      <c r="UH6" s="14"/>
+      <c r="UI6" s="14"/>
+      <c r="UJ6" s="14"/>
+      <c r="UK6" s="14"/>
+      <c r="UL6" s="14"/>
+      <c r="UM6" s="14"/>
+      <c r="UN6" s="14"/>
+      <c r="UO6" s="14"/>
+      <c r="UP6" s="14"/>
+      <c r="UQ6" s="14"/>
+      <c r="UR6" s="14"/>
+      <c r="US6" s="14"/>
+      <c r="UT6" s="14"/>
+      <c r="UU6" s="14"/>
+      <c r="UV6" s="14"/>
+      <c r="UW6" s="14"/>
+      <c r="UX6" s="14"/>
+      <c r="UY6" s="14"/>
+      <c r="UZ6" s="14"/>
+      <c r="VA6" s="14"/>
+      <c r="VB6" s="14"/>
+      <c r="VC6" s="14"/>
+      <c r="VD6" s="14"/>
+      <c r="VE6" s="14"/>
+      <c r="VF6" s="14"/>
+      <c r="VG6" s="14"/>
+      <c r="VH6" s="14"/>
+      <c r="VI6" s="14"/>
+      <c r="VJ6" s="14"/>
+      <c r="VK6" s="14"/>
+      <c r="VL6" s="14"/>
+      <c r="VM6" s="14"/>
+      <c r="VN6" s="14"/>
+      <c r="VO6" s="14"/>
+      <c r="VP6" s="14"/>
+      <c r="VQ6" s="14"/>
+      <c r="VR6" s="14"/>
+      <c r="VS6" s="14"/>
+      <c r="VT6" s="14"/>
+      <c r="VU6" s="14"/>
+      <c r="VV6" s="14"/>
+      <c r="VW6" s="14"/>
+      <c r="VX6" s="14"/>
+      <c r="VY6" s="14"/>
+      <c r="VZ6" s="14"/>
+      <c r="WA6" s="14"/>
+      <c r="WB6" s="14"/>
+      <c r="WC6" s="14"/>
+      <c r="WD6" s="14"/>
+      <c r="WE6" s="14"/>
+      <c r="WF6" s="14"/>
+      <c r="WG6" s="14"/>
+      <c r="WH6" s="14"/>
+      <c r="WI6" s="14"/>
+      <c r="WJ6" s="14"/>
+      <c r="WK6" s="14"/>
+      <c r="WL6" s="14"/>
+      <c r="WM6" s="14"/>
+      <c r="WN6" s="14"/>
+      <c r="WO6" s="14"/>
+      <c r="WP6" s="14"/>
+      <c r="WQ6" s="14"/>
+      <c r="WR6" s="14"/>
+      <c r="WS6" s="14"/>
+      <c r="WT6" s="14"/>
+      <c r="WU6" s="14"/>
+      <c r="WV6" s="14"/>
+      <c r="WW6" s="14"/>
+      <c r="WX6" s="14"/>
+      <c r="WY6" s="14"/>
+      <c r="WZ6" s="14"/>
+      <c r="XA6" s="14"/>
+      <c r="XB6" s="14"/>
+      <c r="XC6" s="14"/>
+      <c r="XD6" s="14"/>
+      <c r="XE6" s="14"/>
+      <c r="XF6" s="14"/>
+      <c r="XG6" s="14"/>
+      <c r="XH6" s="14"/>
+      <c r="XI6" s="14"/>
+      <c r="XJ6" s="14"/>
+      <c r="XK6" s="14"/>
+      <c r="XL6" s="14"/>
+      <c r="XM6" s="14"/>
+      <c r="XN6" s="14"/>
+      <c r="XO6" s="14"/>
+      <c r="XP6" s="14"/>
+      <c r="XQ6" s="14"/>
+      <c r="XR6" s="14"/>
+      <c r="XS6" s="14"/>
+      <c r="XT6" s="14"/>
+      <c r="XU6" s="14"/>
+      <c r="XV6" s="14"/>
+      <c r="XW6" s="14"/>
+      <c r="XX6" s="14"/>
+      <c r="XY6" s="14"/>
+      <c r="XZ6" s="14"/>
+      <c r="YA6" s="14"/>
+      <c r="YB6" s="14"/>
+      <c r="YC6" s="14"/>
+      <c r="YD6" s="14"/>
+      <c r="YE6" s="14"/>
+      <c r="YF6" s="14"/>
+      <c r="YG6" s="14"/>
+      <c r="YH6" s="14"/>
+      <c r="YI6" s="14"/>
+      <c r="YJ6" s="14"/>
+      <c r="YK6" s="14"/>
+      <c r="YL6" s="14"/>
+      <c r="YM6" s="14"/>
+      <c r="YN6" s="14"/>
+      <c r="YO6" s="14"/>
+      <c r="YP6" s="14"/>
+      <c r="YQ6" s="14"/>
+      <c r="YR6" s="14"/>
+      <c r="YS6" s="14"/>
+      <c r="YT6" s="14"/>
+      <c r="YU6" s="14"/>
+      <c r="YV6" s="14"/>
+      <c r="YW6" s="14"/>
+      <c r="YX6" s="14"/>
+      <c r="YY6" s="14"/>
+      <c r="YZ6" s="14"/>
+      <c r="ZA6" s="14"/>
+      <c r="ZB6" s="14"/>
+      <c r="ZC6" s="14"/>
+      <c r="ZD6" s="14"/>
+      <c r="ZE6" s="14"/>
+      <c r="ZF6" s="14"/>
+      <c r="ZG6" s="14"/>
+      <c r="ZH6" s="14"/>
+      <c r="ZI6" s="14"/>
+      <c r="ZJ6" s="14"/>
+      <c r="ZK6" s="14"/>
+      <c r="ZL6" s="14"/>
+      <c r="ZM6" s="14"/>
+      <c r="ZN6" s="14"/>
+      <c r="ZO6" s="14"/>
+      <c r="ZP6" s="14"/>
+      <c r="ZQ6" s="14"/>
+      <c r="ZR6" s="14"/>
+      <c r="ZS6" s="14"/>
+      <c r="ZT6" s="14"/>
+      <c r="ZU6" s="14"/>
+      <c r="ZV6" s="14"/>
+      <c r="ZW6" s="14"/>
+      <c r="ZX6" s="14"/>
+      <c r="ZY6" s="14"/>
+      <c r="ZZ6" s="14"/>
+      <c r="AAA6" s="14"/>
+      <c r="AAB6" s="14"/>
+      <c r="AAC6" s="14"/>
+      <c r="AAD6" s="14"/>
+      <c r="AAE6" s="14"/>
+      <c r="AAF6" s="14"/>
+      <c r="AAG6" s="14"/>
+      <c r="AAH6" s="14"/>
+      <c r="AAI6" s="14"/>
+      <c r="AAJ6" s="14"/>
+      <c r="AAK6" s="14"/>
+      <c r="AAL6" s="14"/>
+      <c r="AAM6" s="14"/>
+      <c r="AAN6" s="14"/>
+      <c r="AAO6" s="14"/>
+      <c r="AAP6" s="14"/>
+      <c r="AAQ6" s="14"/>
+      <c r="AAR6" s="14"/>
+      <c r="AAS6" s="14"/>
+      <c r="AAT6" s="14"/>
+      <c r="AAU6" s="14"/>
+      <c r="AAV6" s="14"/>
+      <c r="AAW6" s="14"/>
+      <c r="AAX6" s="14"/>
+      <c r="AAY6" s="14"/>
+      <c r="AAZ6" s="14"/>
+      <c r="ABA6" s="14"/>
+      <c r="ABB6" s="14"/>
+      <c r="ABC6" s="14"/>
+      <c r="ABD6" s="14"/>
+      <c r="ABE6" s="14"/>
+      <c r="ABF6" s="14"/>
+      <c r="ABG6" s="14"/>
+      <c r="ABH6" s="14"/>
+      <c r="ABI6" s="14"/>
+      <c r="ABJ6" s="14"/>
+      <c r="ABK6" s="14"/>
+      <c r="ABL6" s="14"/>
+      <c r="ABM6" s="14"/>
+      <c r="ABN6" s="14"/>
+      <c r="ABO6" s="14"/>
+      <c r="ABP6" s="14"/>
+      <c r="ABQ6" s="14"/>
+      <c r="ABR6" s="14"/>
+      <c r="ABS6" s="14"/>
+      <c r="ABT6" s="14"/>
+      <c r="ABU6" s="14"/>
+      <c r="ABV6" s="14"/>
+      <c r="ABW6" s="14"/>
+      <c r="ABX6" s="14"/>
+      <c r="ABY6" s="14"/>
+      <c r="ABZ6" s="14"/>
+      <c r="ACA6" s="14"/>
+      <c r="ACB6" s="14"/>
+      <c r="ACC6" s="14"/>
+      <c r="ACD6" s="14"/>
+      <c r="ACE6" s="14"/>
+      <c r="ACF6" s="14"/>
+      <c r="ACG6" s="14"/>
+      <c r="ACH6" s="14"/>
+      <c r="ACI6" s="14"/>
+      <c r="ACJ6" s="14"/>
+      <c r="ACK6" s="14"/>
+      <c r="ACL6" s="14"/>
+      <c r="ACM6" s="14"/>
+      <c r="ACN6" s="14"/>
+      <c r="ACO6" s="14"/>
+      <c r="ACP6" s="14"/>
+      <c r="ACQ6" s="14"/>
+      <c r="ACR6" s="14"/>
+      <c r="ACS6" s="14"/>
+      <c r="ACT6" s="14"/>
+      <c r="ACU6" s="14"/>
+      <c r="ACV6" s="14"/>
+      <c r="ACW6" s="14"/>
+      <c r="ACX6" s="14"/>
+      <c r="ACY6" s="14"/>
+      <c r="ACZ6" s="14"/>
+      <c r="ADA6" s="14"/>
+      <c r="ADB6" s="14"/>
+      <c r="ADC6" s="14"/>
+      <c r="ADD6" s="14"/>
+      <c r="ADE6" s="14"/>
+      <c r="ADF6" s="14"/>
+      <c r="ADG6" s="14"/>
+      <c r="ADH6" s="14"/>
+      <c r="ADI6" s="14"/>
+      <c r="ADJ6" s="14"/>
+      <c r="ADK6" s="14"/>
+      <c r="ADL6" s="14"/>
+      <c r="ADM6" s="14"/>
+      <c r="ADN6" s="14"/>
+      <c r="ADO6" s="14"/>
+      <c r="ADP6" s="14"/>
+      <c r="ADQ6" s="14"/>
+      <c r="ADR6" s="14"/>
+      <c r="ADS6" s="14"/>
+      <c r="ADT6" s="14"/>
+      <c r="ADU6" s="14"/>
+      <c r="ADV6" s="14"/>
+      <c r="ADW6" s="14"/>
+      <c r="ADX6" s="14"/>
+      <c r="ADY6" s="14"/>
+      <c r="ADZ6" s="14"/>
+      <c r="AEA6" s="14"/>
+      <c r="AEB6" s="14"/>
+      <c r="AEC6" s="14"/>
+      <c r="AED6" s="14"/>
+      <c r="AEE6" s="14"/>
+      <c r="AEF6" s="14"/>
+      <c r="AEG6" s="14"/>
+      <c r="AEH6" s="14"/>
+      <c r="AEI6" s="14"/>
+      <c r="AEJ6" s="14"/>
+      <c r="AEK6" s="14"/>
+      <c r="AEL6" s="14"/>
+      <c r="AEM6" s="14"/>
+      <c r="AEN6" s="14"/>
+      <c r="AEO6" s="14"/>
+      <c r="AEP6" s="14"/>
+      <c r="AEQ6" s="14"/>
+      <c r="AER6" s="14"/>
+      <c r="AES6" s="14"/>
+      <c r="AET6" s="14"/>
+      <c r="AEU6" s="14"/>
+      <c r="AEV6" s="14"/>
+      <c r="AEW6" s="14"/>
+      <c r="AEX6" s="14"/>
+      <c r="AEY6" s="14"/>
+      <c r="AEZ6" s="14"/>
+      <c r="AFA6" s="14"/>
+      <c r="AFB6" s="14"/>
+      <c r="AFC6" s="14"/>
+      <c r="AFD6" s="14"/>
+      <c r="AFE6" s="14"/>
+      <c r="AFF6" s="14"/>
+      <c r="AFG6" s="14"/>
+      <c r="AFH6" s="14"/>
+      <c r="AFI6" s="14"/>
+      <c r="AFJ6" s="14"/>
+      <c r="AFK6" s="14"/>
+      <c r="AFL6" s="14"/>
+      <c r="AFM6" s="14"/>
+      <c r="AFN6" s="14"/>
+      <c r="AFO6" s="14"/>
+      <c r="AFP6" s="14"/>
+      <c r="AFQ6" s="14"/>
+      <c r="AFR6" s="14"/>
+      <c r="AFS6" s="14"/>
+      <c r="AFT6" s="14"/>
+      <c r="AFU6" s="14"/>
+      <c r="AFV6" s="14"/>
+      <c r="AFW6" s="14"/>
+      <c r="AFX6" s="14"/>
+      <c r="AFY6" s="14"/>
+      <c r="AFZ6" s="14"/>
+      <c r="AGA6" s="14"/>
+      <c r="AGB6" s="14"/>
+      <c r="AGC6" s="14"/>
+      <c r="AGD6" s="14"/>
+      <c r="AGE6" s="14"/>
+      <c r="AGF6" s="14"/>
+      <c r="AGG6" s="14"/>
+      <c r="AGH6" s="14"/>
+      <c r="AGI6" s="14"/>
+      <c r="AGJ6" s="14"/>
+      <c r="AGK6" s="14"/>
+      <c r="AGL6" s="14"/>
+      <c r="AGM6" s="14"/>
+      <c r="AGN6" s="14"/>
+      <c r="AGO6" s="14"/>
+      <c r="AGP6" s="14"/>
+      <c r="AGQ6" s="14"/>
+      <c r="AGR6" s="14"/>
+      <c r="AGS6" s="14"/>
+      <c r="AGT6" s="14"/>
+      <c r="AGU6" s="14"/>
+      <c r="AGV6" s="14"/>
+      <c r="AGW6" s="14"/>
+      <c r="AGX6" s="14"/>
+      <c r="AGY6" s="14"/>
+      <c r="AGZ6" s="14"/>
+      <c r="AHA6" s="14"/>
+      <c r="AHB6" s="14"/>
+      <c r="AHC6" s="14"/>
+      <c r="AHD6" s="14"/>
+      <c r="AHE6" s="14"/>
+      <c r="AHF6" s="14"/>
+      <c r="AHG6" s="14"/>
+      <c r="AHH6" s="14"/>
+      <c r="AHI6" s="14"/>
+      <c r="AHJ6" s="14"/>
+      <c r="AHK6" s="14"/>
+      <c r="AHL6" s="14"/>
+      <c r="AHM6" s="14"/>
+      <c r="AHN6" s="14"/>
+      <c r="AHO6" s="14"/>
+      <c r="AHP6" s="14"/>
+      <c r="AHQ6" s="14"/>
+      <c r="AHR6" s="14"/>
+      <c r="AHS6" s="14"/>
+      <c r="AHT6" s="14"/>
+      <c r="AHU6" s="14"/>
+      <c r="AHV6" s="14"/>
+      <c r="AHW6" s="14"/>
+      <c r="AHX6" s="14"/>
+      <c r="AHY6" s="14"/>
+      <c r="AHZ6" s="14"/>
+      <c r="AIA6" s="14"/>
+      <c r="AIB6" s="14"/>
+      <c r="AIC6" s="14"/>
+      <c r="AID6" s="14"/>
+      <c r="AIE6" s="14"/>
+      <c r="AIF6" s="14"/>
+      <c r="AIG6" s="14"/>
+      <c r="AIH6" s="14"/>
+      <c r="AII6" s="14"/>
+      <c r="AIJ6" s="14"/>
+      <c r="AIK6" s="14"/>
+      <c r="AIL6" s="14"/>
+      <c r="AIM6" s="14"/>
+      <c r="AIN6" s="14"/>
+      <c r="AIO6" s="14"/>
+      <c r="AIP6" s="14"/>
+      <c r="AIQ6" s="14"/>
+      <c r="AIR6" s="14"/>
+      <c r="AIS6" s="14"/>
+      <c r="AIT6" s="14"/>
+      <c r="AIU6" s="14"/>
+      <c r="AIV6" s="14"/>
+      <c r="AIW6" s="14"/>
+      <c r="AIX6" s="14"/>
+      <c r="AIY6" s="14"/>
+      <c r="AIZ6" s="14"/>
+      <c r="AJA6" s="14"/>
+      <c r="AJB6" s="14"/>
+      <c r="AJC6" s="14"/>
+      <c r="AJD6" s="14"/>
+      <c r="AJE6" s="14"/>
+      <c r="AJF6" s="14"/>
+      <c r="AJG6" s="14"/>
+      <c r="AJH6" s="14"/>
+      <c r="AJI6" s="14"/>
+      <c r="AJJ6" s="14"/>
+      <c r="AJK6" s="14"/>
+      <c r="AJL6" s="14"/>
+      <c r="AJM6" s="14"/>
+      <c r="AJN6" s="14"/>
+      <c r="AJO6" s="14"/>
+      <c r="AJP6" s="14"/>
+      <c r="AJQ6" s="14"/>
+      <c r="AJR6" s="14"/>
+      <c r="AJS6" s="14"/>
+      <c r="AJT6" s="14"/>
+      <c r="AJU6" s="14"/>
+      <c r="AJV6" s="14"/>
+      <c r="AJW6" s="14"/>
+      <c r="AJX6" s="14"/>
+      <c r="AJY6" s="14"/>
+      <c r="AJZ6" s="14"/>
+      <c r="AKA6" s="14"/>
+      <c r="AKB6" s="14"/>
+      <c r="AKC6" s="14"/>
+      <c r="AKD6" s="14"/>
+      <c r="AKE6" s="14"/>
+      <c r="AKF6" s="14"/>
+      <c r="AKG6" s="14"/>
+      <c r="AKH6" s="14"/>
+      <c r="AKI6" s="14"/>
+      <c r="AKJ6" s="14"/>
+      <c r="AKK6" s="14"/>
+      <c r="AKL6" s="14"/>
+      <c r="AKM6" s="14"/>
+      <c r="AKN6" s="14"/>
+      <c r="AKO6" s="14"/>
+      <c r="AKP6" s="14"/>
+      <c r="AKQ6" s="14"/>
+      <c r="AKR6" s="14"/>
+      <c r="AKS6" s="14"/>
+      <c r="AKT6" s="14"/>
+      <c r="AKU6" s="14"/>
+      <c r="AKV6" s="14"/>
+      <c r="AKW6" s="14"/>
+      <c r="AKX6" s="14"/>
+      <c r="AKY6" s="14"/>
+      <c r="AKZ6" s="14"/>
+      <c r="ALA6" s="14"/>
+      <c r="ALB6" s="14"/>
+      <c r="ALC6" s="14"/>
+      <c r="ALD6" s="14"/>
+      <c r="ALE6" s="14"/>
+      <c r="ALF6" s="14"/>
+      <c r="ALG6" s="14"/>
+      <c r="ALH6" s="14"/>
+      <c r="ALI6" s="14"/>
+      <c r="ALJ6" s="14"/>
+      <c r="ALK6" s="14"/>
+      <c r="ALL6" s="14"/>
+      <c r="ALM6" s="14"/>
+      <c r="ALN6" s="14"/>
+      <c r="ALO6" s="14"/>
+      <c r="ALP6" s="14"/>
+      <c r="ALQ6" s="14"/>
+      <c r="ALR6" s="14"/>
+      <c r="ALS6" s="14"/>
+      <c r="ALT6" s="14"/>
+      <c r="ALU6" s="14"/>
+      <c r="ALV6" s="14"/>
+      <c r="ALW6" s="14"/>
+      <c r="ALX6" s="14"/>
+      <c r="ALY6" s="14"/>
+      <c r="ALZ6" s="14"/>
+      <c r="AMA6" s="14"/>
+      <c r="AMB6" s="14"/>
+      <c r="AMC6" s="14"/>
+      <c r="AMD6" s="14"/>
+      <c r="AME6" s="14"/>
+      <c r="AMF6" s="14"/>
+      <c r="AMG6" s="14"/>
+      <c r="AMH6" s="14"/>
+      <c r="AMI6" s="14"/>
+      <c r="AMJ6" s="14"/>
+      <c r="AMK6" s="14"/>
     </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
+    <row r="7" spans="1:1024 1025:1025">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
